--- a/system_development/V0.2/Optical Table CAD Files/Helmholtz Cage Assembly/Quick Spacing Calculations.xlsx
+++ b/system_development/V0.2/Optical Table CAD Files/Helmholtz Cage Assembly/Quick Spacing Calculations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAB1\Documents\GitHub\Fieldable-NV-Center\system_development\V0.2\Optical Table CAD Files\Helmholtz Cage Assembly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8816477F-11A2-4DF7-ADA8-4604F23BCD6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC64429-3A2A-4236-BB1E-FBC7881FC0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{430E4448-000C-42A0-B3A6-C78EC43BEFCD}"/>
   </bookViews>
@@ -38,8 +38,66 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Bailey, Patrick</author>
+  </authors>
+  <commentList>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{07B974CD-6F96-472E-AAFD-90E1A7132D3E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Bailey, Patrick:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Different internal length spacings are needed because 1 side of each of the brackets has the 2.1mm spacer that adds on to its total length for that side</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{4F270678-22A5-4A67-8F5E-F6FB2B5B5D0D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Bailey, Patrick:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Different internal length spacings are needed because 1 side of each of the brackets has the 2.1mm spacer that adds on to its total length for that side</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="26">
   <si>
     <t>Ls</t>
   </si>
@@ -102,19 +160,47 @@
   </si>
   <si>
     <t>5.2mT</t>
+  </si>
+  <si>
+    <t>Old Values (Incorrect E and Gap Calculations)</t>
+  </si>
+  <si>
+    <t>Spacer</t>
+  </si>
+  <si>
+    <t>Tl</t>
+  </si>
+  <si>
+    <t>half internal length for snap side</t>
+  </si>
+  <si>
+    <t>half internal length for normal side</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -154,6 +240,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -472,14 +562,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F54EA13F-0CE6-4602-A8D7-9EFDABB40DFA}">
-  <dimension ref="A1:H25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F54EA13F-0CE6-4602-A8D7-9EFDABB40DFA}">
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -493,25 +584,28 @@
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>B2*2/0.5445</f>
         <v>302.40000000000003</v>
       </c>
       <c r="B2">
-        <f>(C2+D2*2-E2)*0.5445*0.5</f>
+        <f>(C2+D2*2-F2)*0.5445*0.5</f>
         <v>82.328400000000002</v>
       </c>
       <c r="C2">
@@ -521,22 +615,25 @@
         <v>26.4</v>
       </c>
       <c r="E2">
+        <v>2.1</v>
+      </c>
+      <c r="F2">
         <v>25.4</v>
       </c>
-      <c r="F2">
-        <f>C2+2*D2</f>
-        <v>327.8</v>
-      </c>
       <c r="G2">
-        <f>E2+2</f>
-        <v>27.4</v>
-      </c>
-      <c r="H2">
-        <f>(F2-2*E2)*0.5</f>
+        <f>C2+2*(D2+E2)</f>
+        <v>332</v>
+      </c>
+      <c r="I2">
+        <f>(G2-2*(F2+E2))*0.5</f>
         <v>138.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <f>(G2-2*F2)*0.5</f>
+        <v>140.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
@@ -547,44 +644,50 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>B4*2/0.5445</f>
-        <v>357.20000000000005</v>
+        <v>357.40000000000003</v>
       </c>
       <c r="B4">
-        <f>(C4+D4*2-E4)*0.5445*0.5</f>
-        <v>97.247700000000009</v>
+        <f>(C4+D4*2-F4)*0.5445*0.5</f>
+        <v>97.302150000000012</v>
       </c>
       <c r="C4">
-        <f>F4-2*D4</f>
-        <v>329.8</v>
+        <f>G4-2*(D4+E4)</f>
+        <v>330</v>
       </c>
       <c r="D4">
         <v>26.4</v>
       </c>
       <c r="E4">
+        <v>2.1</v>
+      </c>
+      <c r="F4">
         <v>25.4</v>
       </c>
-      <c r="F4">
-        <f>F2+2*G2</f>
-        <v>382.6</v>
-      </c>
-      <c r="H4">
-        <f>(F4-2*E4)*0.5</f>
-        <v>165.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <f>G2+2*(F4+E4)</f>
+        <v>387</v>
+      </c>
+      <c r="I4">
+        <f>(G4-2*(F4+E4))*0.5</f>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -595,44 +698,47 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
         <v>2</v>
       </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>B6*2/0.5445</f>
-        <v>412.00000000000006</v>
+        <v>412.40000000000003</v>
       </c>
       <c r="B6">
-        <f>(C6+D6*2-E6)*0.5445*0.5</f>
-        <v>112.16700000000002</v>
+        <f>(C6+D6*2-F6)*0.5445*0.5</f>
+        <v>112.27590000000001</v>
       </c>
       <c r="C6">
-        <f>F6-2*D6</f>
-        <v>384.6</v>
+        <f>G6-2*D6</f>
+        <v>385</v>
       </c>
       <c r="D6">
         <v>26.4</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>25.4</v>
       </c>
-      <c r="F6">
-        <f>F4+2*G2</f>
-        <v>437.40000000000003</v>
-      </c>
-      <c r="H6">
-        <f>(F6-2*E6)*0.5</f>
-        <v>193.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <f>G4+2*(F6+E6)</f>
+        <v>437.8</v>
+      </c>
+      <c r="I6">
+        <f>(G6-2*F6)*0.5</f>
+        <v>193.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>97</v>
       </c>
@@ -645,12 +751,153 @@
         <v>3.3188976377952755</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C11">
         <v>69.581000000000003</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="K11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" t="s">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P12" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K13">
+        <v>302.40000000000003</v>
+      </c>
+      <c r="L13">
+        <v>82.328400000000002</v>
+      </c>
+      <c r="M13">
+        <v>275</v>
+      </c>
+      <c r="N13">
+        <v>26.4</v>
+      </c>
+      <c r="O13">
+        <v>25.4</v>
+      </c>
+      <c r="P13">
+        <v>327.8</v>
+      </c>
+      <c r="Q13">
+        <v>27.5</v>
+      </c>
+      <c r="R13">
+        <v>138.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L14" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P14" t="s">
+        <v>9</v>
+      </c>
+      <c r="R14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K15">
+        <v>357.40000000000003</v>
+      </c>
+      <c r="L15">
+        <v>97.302150000000012</v>
+      </c>
+      <c r="M15">
+        <v>330</v>
+      </c>
+      <c r="N15">
+        <v>26.4</v>
+      </c>
+      <c r="O15">
+        <v>25.4</v>
+      </c>
+      <c r="P15">
+        <v>382.8</v>
+      </c>
+      <c r="R15">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L16" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" t="s">
+        <v>6</v>
+      </c>
+      <c r="N16" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" t="s">
+        <v>2</v>
+      </c>
+      <c r="P16" t="s">
+        <v>9</v>
+      </c>
+      <c r="R16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <v>412.40000000000003</v>
+      </c>
+      <c r="L17">
+        <v>112.27590000000001</v>
+      </c>
+      <c r="M17">
+        <v>385</v>
+      </c>
+      <c r="N17">
+        <v>26.4</v>
+      </c>
+      <c r="O17">
+        <v>25.4</v>
+      </c>
+      <c r="P17">
+        <v>437.8</v>
+      </c>
+      <c r="R17">
+        <v>193.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>13</v>
       </c>
@@ -658,7 +905,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>12</v>
       </c>
@@ -669,7 +916,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>17</v>
       </c>
@@ -677,7 +924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>19</v>
       </c>
@@ -693,5 +940,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>